--- a/business_forms/042_inside_sales_call_report_form--business_forms.xlsx
+++ b/business_forms/042_inside_sales_call_report_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>inside_sales_call_report_form_1</t>
+          <t>first_contact</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_call</t>
+          <t>First Contact</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>inside_sales_call_report_form_2</t>
+          <t>customer_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>inside_sales_call_report_form_3</t>
+          <t>product_or_service</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>Product or Service</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>inside_sales_call_report_form_4</t>
+          <t>next_contact_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>Next Contact Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>inside_sales_call_report_form_5</t>
+          <t>follow_up_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>product_or_service</t>
+          <t>Follow-up Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>inside_sales_call_report_form_6</t>
+          <t>follow_up_method</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>next_call</t>
+          <t>Follow-up Method</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>inside_sales_call_report_form_7</t>
+          <t>customer_response</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>next_call</t>
+          <t>Customer Response</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>inside_sales_call_report_form_8</t>
+          <t>follow_up_action</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>follow_up_date</t>
+          <t>Follow-up Action</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>inside_sales_call_report_form_9</t>
+          <t>outcome</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>follow_up_date</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,90 +722,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>inside_sales_call_report_form_10</t>
+          <t>follow_up_outcome</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>Follow-up Outcome</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>inside_sales_call_report_form_11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>inside_sales_call_report_form_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>customer_call_result</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>inside_sales_call_report_form_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,11 +753,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -850,102 +781,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>inside_sales_call_report_form_3_choices</t>
+          <t>first_contact_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>inside_sales_call_report_form_3_choices</t>
+          <t>first_contact_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>inside_sales_call_report_form_4_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>inside_sales_call_report_form_4_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>inside_sales_call_report_form_12_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>inside_sales_call_report_form_12_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
